--- a/basedatos_partidas/salida/descompuestos/07.05.02.140.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.05.02.140.xlsx
@@ -584,10 +584,10 @@
         <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.15</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16.19</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="15">
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>22.67</v>
+        <v>22.83</v>
       </c>
       <c r="H24" t="n">
         <v>0.23</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>22.9</v>
+        <v>23.06</v>
       </c>
     </row>
   </sheetData>
